--- a/reviews/a-envoyer/pierre-huiban-2026-10-19.xlsx
+++ b/reviews/a-envoyer/pierre-huiban-2026-10-19.xlsx
@@ -723,7 +723,7 @@
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>Post</t>
+          <t>Story</t>
         </is>
       </c>
       <c r="E2" s="6" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>Post</t>
+          <t>Story</t>
         </is>
       </c>
       <c r="E3" s="6" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>Post</t>
+          <t>Story</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>Post</t>
+          <t>Story</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>Post</t>
+          <t>Story</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>Post</t>
+          <t>Story</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>Post</t>
+          <t>Story</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-09T06:25:11</t>
+          <t>2026-10-12T08:14:38</t>
         </is>
       </c>
     </row>

--- a/reviews/a-envoyer/pierre-huiban-2026-10-19.xlsx
+++ b/reviews/a-envoyer/pierre-huiban-2026-10-19.xlsx
@@ -1221,7 +1221,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-12T08:14:38</t>
+          <t>2026-10-16T06:15:54</t>
         </is>
       </c>
     </row>

--- a/reviews/a-envoyer/pierre-huiban-2026-10-19.xlsx
+++ b/reviews/a-envoyer/pierre-huiban-2026-10-19.xlsx
@@ -1221,7 +1221,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-16T06:15:54</t>
+          <t>2026-10-16T09:35:23</t>
         </is>
       </c>
     </row>
